--- a/歌词翻译/op001_歌词对照.xlsx
+++ b/歌词翻译/op001_歌词对照.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="23040" windowHeight="10500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="歌词对照" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="歌词对照" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>那此刻的天候呢？</t>
+          <t>那此刻的天气呢？</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
